--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -574,8 +574,10 @@
           <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>7207250142</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,8 +605,10 @@
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>4500011424</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4500011424</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -630,7 +634,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -707,7 +711,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+          <t>Moh Bazarul Aqhsa / Imron Maulana</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -717,7 +721,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-16 20:17:09</t>
+          <t>2026-08-17 10:31:57</t>
         </is>
       </c>
     </row>
@@ -727,10 +731,8 @@
           <t>043/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="B3" t="n">
+        <v>7207250142</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -758,10 +760,8 @@
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>4500011425</t>
-        </is>
+      <c r="H3" t="n">
+        <v>4500011425</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,7 +660,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>General Service Manager</t>
+          <t>Manager General Services</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -716,12 +716,12 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Field Senior Manager</t>
+          <t>Maintenance Superintendent</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-17 10:31:57</t>
+          <t>2026-08-18 15:08:23</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>General Service Manager</t>
+          <t>Manager General Services</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -869,12 +869,165 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Field Senior Manager</t>
+          <t>Maintenance Superintendet</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-08-16 20:21:00</t>
+          <t>2026-08-18 15:07:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
+</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>16 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4500011426</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1 Jul 2026</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">J“Jasa Sewa Vacuum TruckUntuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-021" (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
+</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WCC-2026-021</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-021</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Vacuum Truck  untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-CTR-2026-021</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendet</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-08-18 15:06:55</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -574,10 +574,8 @@
           <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -605,10 +603,8 @@
           <t>31 Jul 2026</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="H2" t="n">
+        <v>4500011424</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -623,7 +619,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+          <t>JOB Pertamina</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -721,7 +717,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-18 15:08:23</t>
+          <t>2026-08-18 18:34:09</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>JOB Pertamina</t>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+          <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -645,8 +645,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
-</t>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -707,7 +706,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Moh Bazarul Aqhsa / Imron Maulana</t>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -717,313 +716,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-18 18:34:09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7207250142</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S250551FLD-R1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>16 Desember 2025</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4500011425</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1 Jul 2026</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
-</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Maintenance Support Supervisor</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>PT Banggai Sentral Sulawesi</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
-</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Ir. Ferry Tatimu</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>01 s/d 31 Juli 2026</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-WCC-2026-020</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-WO-2026-020</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
-</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-CTR-2026-020</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Onesimus Suriadi</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Manager General Services</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Maintenance Superintendet</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2026-08-18 15:07:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>044/BSS-JOB/AB/VII/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>7207250142</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S250551FLD-R1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>16 Desember 2025</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4500011426</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1 Jul 2026</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">J“Jasa Sewa Vacuum TruckUntuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-021" (01 - 31 Juli 2026)
-</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Maintenance Support Supervisor</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>PT Banggai Sentral Sulawesi</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Ir. Ferry Tatimu</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>01 s/d 31 Juli 2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-WCC-2026-021</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-WO-2026-021</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Vacuum Truck  untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
-</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-CTR-2026-021</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Onesimus Suriadi</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Manager General Services</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Maintenance Superintendet</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2026-08-18 15:06:55</t>
+          <t>2026-08-19 19:58:12</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,154 +413,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Proforma Invoice No.</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nomor Kontrak</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Nomor Tender</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Judul Kontrak</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Tanggal Kontrak</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Jangka Waktu Kontrak</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Tanggal Performa Invoice</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Nomor Purchase Order</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Tanggal Purchase Order</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Lingkup Pekerjaan</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Pihak Pertama</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Alamat Pihak Pertama</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Diwakili Oleh</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Selaku</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Pihak Kedua</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Alamat Pihak Kedua</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Diwakili Oleh (P2)</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Selaku (P2)</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Periode Pekerjaan</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Nomor WCC</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Tanggal WCC</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Nomor WO</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Keterangan WO</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Nomor CTR</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Progress Pekerjaan</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Prepared by Name</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Prepared by Title</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Pejabat berwenang</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Jabatan Field Manager</t>
-        </is>
+      <c r="A1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+      <c r="N1" t="n">
+        <v>13</v>
+      </c>
+      <c r="O1" t="n">
+        <v>14</v>
+      </c>
+      <c r="P1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="n">
+        <v>16</v>
+      </c>
+      <c r="R1" t="n">
+        <v>17</v>
+      </c>
+      <c r="S1" t="n">
+        <v>18</v>
+      </c>
+      <c r="T1" t="n">
+        <v>19</v>
+      </c>
+      <c r="U1" t="n">
+        <v>20</v>
+      </c>
+      <c r="V1" t="n">
+        <v>21</v>
+      </c>
+      <c r="W1" t="n">
+        <v>22</v>
+      </c>
+      <c r="X1" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="n">
+        <v>28</v>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
@@ -574,8 +516,10 @@
           <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>7207250142</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -583,38 +527,40 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>16 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
 </t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>16 Desember 2025</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>31 Jul 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4500011424</v>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>4500011424</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>1 Jul 2026</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
-</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -716,7 +662,159 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-19 19:58:12</t>
+          <t>2026-08-20 16:14:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7207250142</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>16 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
+</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4500011425</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1 Jul 2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WCC-2026-019</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-019</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
+</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-CTR-2026-019</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:14:10</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,10 +516,8 @@
           <t>042/BSS-JOB/AB/VII/2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7207250142</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7207250142</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -553,10 +551,8 @@
 </t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4500011424</t>
-        </is>
+      <c r="I2" t="n">
+        <v>4500011424</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -662,7 +658,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-20 16:14:10</t>
+          <t>2026-08-21 16:00:46</t>
         </is>
       </c>
     </row>
@@ -814,7 +810,135 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-08-20 16:14:10</t>
+          <t>2026-08-21 16:00:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>010/BSS-JOB/WH/VII/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S250009SCM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton
+</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9 Juni 2025</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>03 Desember 2027</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
+</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2 Januari 2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
+</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Irwan / Budi Bernadi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MM Operation Supervisor</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
+</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-08-21 16:00:46</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -658,7 +658,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:46</t>
+          <t>2026-08-21 21:16:30</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WCC-2026-019</t>
+          <t>7207250142-BSS-WCC-2026-020</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-019</t>
+          <t>7207250142-BSS-WO-2026-020</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>7207250142-BSS-CTR-2026-019</t>
+          <t>7207250142-BSS-CTR-2026-020</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:46</t>
+          <t>2026-08-21 21:16:30</t>
         </is>
       </c>
     </row>
@@ -832,8 +832,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton
-</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -914,12 +913,36 @@
           <t>01 s/d 31 Juli 2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2 Januari 2026</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr">
         <is>
           <t>Onesimus Suriadi</t>
@@ -935,10 +958,14 @@
           <t>Imron Maulana / Moh Bazarul Aqhsa</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:46</t>
+          <t>2026-08-21 21:16:30</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,13 @@
       <c r="AC1" t="n">
         <v>28</v>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Update Terakhir</t>
         </is>
@@ -526,8 +532,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)
-</t>
+          <t>Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -547,8 +552,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -566,8 +570,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -622,8 +625,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
-</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -648,7 +650,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+          <t>--- (Tidak Ada / Kosong) ---</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -658,7 +660,17 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-21 21:16:30</t>
+          <t>Abidsar</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>Senior Field Manager</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-08-23 22:15:28</t>
         </is>
       </c>
     </row>
@@ -808,9 +820,11 @@
           <t>Maintenance Superintendent</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:16:30</t>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2026-08-23 22:15:28</t>
         </is>
       </c>
     </row>
@@ -820,10 +834,8 @@
           <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7203250036</t>
-        </is>
+      <c r="B4" t="n">
+        <v>7203250036</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -852,120 +864,379 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Penyediaan Jasa Penyewaan Alat Berat Werehouse
-</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4500010848</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2 Januari 2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Irwan / Budi Bernadi</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MM Operation Supervisor</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>01 s/d 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4500010848</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>2 Januari 2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Irwan / Budi Bernadi</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>MM Operation Supervisor</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2026-08-23 22:15:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>17 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Irwan / Budi Bernadi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>MM Operation Supervisor</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>PT Banggai Sentral Sulawesi</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia
-</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Ir. Ferry Tatimu</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Direktur</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>01 s/d 31 Juli 2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2 Januari 2026</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>18 sd 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>Onesimus Suriadi</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Manager General Services</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2026-08-23 22:15:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>20 Juni 2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>15 Juli sd 03 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Imron Maulana / Moh Bazarul Aqhsa</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:16:30</t>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2026-08-23 22:15:28</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-23 22:15:28</t>
+          <t>2026-08-24 11:56:33</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-23 22:15:28</t>
+          <t>2026-08-24 11:56:33</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-23 22:15:28</t>
+          <t>2026-08-24 11:56:33</t>
         </is>
       </c>
     </row>
@@ -988,10 +988,8 @@
           <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="B5" t="n">
+        <v>7201250141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,7 +1110,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-23 22:15:28</t>
+          <t>2026-08-24 11:56:33</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1234,425 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-23 22:15:28</t>
+          <t>2026-08-24 11:56:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>008/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>17 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>09 Juli 2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>18 sd 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>008/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>09 Juli 2026</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:56:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>18 sd 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:56:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>17 Desember 2025</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>18 sd 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2026-08-24 11:56:33</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -519,11 +519,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/AB/VII/2026</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>7207250142</v>
+          <t>043/BSS-JOB/AB/VII/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -532,7 +534,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-019" (01 - 31 Juli 2026)</t>
+          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -555,8 +557,10 @@
           <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>4500011424</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4500011425</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -575,7 +579,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Ronny Dwi Purnomo / Rafik Hidayat</t>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -610,7 +614,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WCC-2026-019</t>
+          <t>7207250142-BSS-WCC-2026-020</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -620,17 +624,17 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-019</t>
+          <t>7207250142-BSS-WO-2026-020</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>7207250142-BSS-CTR-2026-019</t>
+          <t>7207250142-BSS-CTR-2026-020</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -650,7 +654,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>--- (Tidak Ada / Kosong) ---</t>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -658,50 +662,43 @@
           <t>Maintenance Superintendent</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Abidsar</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Senior Field Manager</t>
-        </is>
-      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>7207250142</v>
+          <t>010/BSS-JOB/WH/VII/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7203250036</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)
-</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16 Desember 2025</t>
+          <t>9 Juni 2025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -711,16 +708,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka
-</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4500011425</v>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4500010848</t>
+        </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -730,18 +728,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia
-</t>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+          <t>Irwan / Budi Bernadi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Maintenance Support Supervisor</t>
+          <t>MM Operation Supervisor</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -751,7 +748,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -771,28 +768,27 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WCC-2026-020</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>2 Januari 2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)
-</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>7207250142-BSS-CTR-2026-020</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -812,67 +808,71 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+          <t>Irwan / Budi Bernadi</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Maintenance Superintendent</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+          <t>MM Operation Supervisor</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>7203250036</v>
+          <t>005/BSS-JOB/WS/V/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9 Juni 2025</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>4500010848</v>
-      </c>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Irwan / Budi Bernadi</t>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MM Operation Supervisor</t>
+          <t>Contract Engineer</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -917,34 +917,26 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01 s/d 31 Juli 2026</t>
+          <t>18 sd 20 Mei 2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
           <t>100%</t>
@@ -962,12 +954,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Irwan / Budi Bernadi</t>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>MM Operation Supervisor</t>
+          <t>Contract Engineer</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -978,18 +970,20 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7201250141</v>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,7 +992,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1065,12 +1059,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>18 sd 20 Mei 2026</t>
+          <t>15 Juli sd 03 Agustus 2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -1094,34 +1088,28 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Contract Engineer</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>--- (Tidak Ada / Kosong) ---</t>
-        </is>
-      </c>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>7201250141</v>
+          <t>008/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,12 +1118,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17 Desember 2025</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1145,7 +1133,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,7 +1142,11 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>06 Jul 2026</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
@@ -1197,17 +1189,25 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>15 Juli sd 03 Agustus 2026</t>
+          <t>06 sd 09 Juli 2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr"/>
+          <t>008/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>09 Jul 2026</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1226,26 +1226,36 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>7201250141</v>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,12 +1264,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17 Desember 2025</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1269,7 +1279,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>09 Juli 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,7 +1288,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
@@ -1321,21 +1335,29 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>18 sd 20 Mei 2026</t>
+          <t>03 sd 04 Agustus 2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>09 Juli 2026</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1370,18 +1392,20 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7201250141</v>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,12 +1414,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17 Desember 2025</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1405,7 +1429,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1413,8 +1437,16 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
@@ -1462,16 +1494,20 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>4 Agustus 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1506,14 +1542,14 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1528,7 +1564,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Data Uji Coba</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1553,7 +1589,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011587</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1608,7 +1644,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1652,7 +1688,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-08-24 11:56:33</t>
+          <t>2026-08-25 19:59:50</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -666,7 +666,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17 Desember 2025</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20 Juni 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1016,7 +1016,11 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
@@ -1059,17 +1063,25 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>15 Juli sd 03 Agustus 2026</t>
+          <t>15 Juli sd 11 Agustus 2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>11 Aug 2026</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1092,11 +1104,15 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1258,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1408,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1558,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1704,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-08-25 19:59:50</t>
+          <t>2026-08-25 22:09:33</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -1435,17 +1435,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>18 sd 20 Mei 2026</t>
+          <t>5 Agustus  2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -1558,7 +1558,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,157 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-08-25 22:09:33</t>
+          <t>2026-08-26 15:15:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4500011587</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5 Agustus  2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2026-08-26 15:15:44</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,157 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-08-26 15:15:44</t>
+          <t>2026-08-26 18:26:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pembelian Material dan Pengiriman barang ke Lokasi Senoro </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4500011588</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5 Agustus  2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pembelian Material dan Pengiriman barang ke Lokasi Senoro </t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2026-08-26 18:26:01</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -666,7 +666,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9 Juni 2025</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Irwan / Budi Bernadi</t>
+          <t>Budi Bernadi / Irwan</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pembelian Material dan Pengiriman barang ke Lokasi Senoro </t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1967,7 +1967,7 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pembelian Material dan Pengiriman barang ke Lokasi Senoro </t>
+          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-08-26 18:26:01</t>
+          <t>2026-08-27 15:19:06</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,157 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-08-27 15:19:06</t>
+          <t>2026-09-07 12:43:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>001/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4500011581</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>17 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>001/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>17 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:43:18</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,7 +666,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,149 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:43:18</t>
+          <t>2026-09-07 20:42:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>014A/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>01 Jul 2026</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>28 sd 31 Juli 2026</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>014A/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>31 Jul 2026</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2026-09-07 20:42:32</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16 Desember 2025</t>
+          <t>08 Sep 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1 Jul 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -662,11 +662,15 @@
           <t>Maintenance Superintendent</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -824,7 +828,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -970,7 +974,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1116,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1262,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1412,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1562,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1708,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1858,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2008,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2158,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2300,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-07 20:42:32</t>
+          <t>2026-09-08 06:53:38</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1584,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data Uji Coba</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17 Desember 2025</t>
+          <t>08 Sep 2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1607,14 +1607,10 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4500011587</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1659,7 +1655,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>18 sd 20 Mei 2026</t>
+          <t>16 Agustus 2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1669,11 +1665,15 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5 Agustus 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1753,14 +1753,10 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4500011587</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1805,7 +1801,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>5 Agustus  2026</t>
+          <t>8 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1815,13 +1811,13 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Pembelian Material Kabel dan Kayu untuk senoro</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1858,7 +1854,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1891,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1903,14 +1899,10 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4500011588</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1955,7 +1947,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>5 Agustus  2026</t>
+          <t>25  Agustus  2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1965,7 +1957,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -2008,7 +2000,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2150,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2292,307 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-08 06:53:38</t>
+          <t>2026-09-08 11:31:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>17 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:31:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>30 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:31:48</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF15"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1899,10 +1899,14 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4500011682</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1963,7 +1967,7 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Pembelian Material dan Pengiriman barang ke Lokasi Senoro</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -2000,7 +2004,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2154,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2296,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2446,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2596,1061 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:48</t>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4500011683</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>25  Agustus  2026</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>4500011683</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>25  Agustus  2026</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>4500011683</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>10 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>023/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4 September 2026</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>024/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>2026-09-09 15:37:40</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>Periode tanggal 8 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3500,7 +3500,7 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>Periode Tanggal 8 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -3650,7 +3650,1357 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-09 15:37:40</t>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>025/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>06 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Periode tanggal 07 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>026/BSS-JOB/WS/VII/2026</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Periode tanggal 07 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/WS/IV/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>28 Apr 2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4500011236</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>18 Feb 2026</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026/04/28</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/WS/IV/2026</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>28 Apr 2026</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4500011203</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>19 Februari 2026</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/WS/II/2026</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>19 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>006/BSS-JOB/WS/VI/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4500011579</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>04 Jun 2026</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>18 sd 20 Mei 2026</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>006/BSS-JOB/WS/VI/2026</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>007/BSS-JOB/WS/VI/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>17 Dec 2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>4500011580</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>04 Jun 2026</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Periode tanggal 6 Juni 2026</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>007/BSS-JOB/WS/VI/2026</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>06 Jun 2026</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:41:11</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_proforma_invoice.xlsx
+++ b/database_penyimpanan_aman/database_proforma_invoice.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF31"/>
+  <dimension ref="A1:AF47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,32 +519,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/AB/VII/2026</t>
+          <t>010/BSS-JOB/WH/VII/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7207250142</t>
+          <t>7203250036</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S250009SCM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift Untuk support Kegiatan Operation &amp; Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026, Refer CTR No. 7207250142-BSS-CTR-2026-020" (01 - 31 Juli 2026)</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08 Sep 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24 Month</t>
+          <t>03 Desember 2027</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -554,17 +554,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4500011425</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+          <t>Budi Bernadi / Irwan</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Maintenance Support Supervisor</t>
+          <t>MM Operation Supervisor</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -614,27 +614,27 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WCC-2026-020</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode Juli - September 2026 (01 - 31 Juli 2026)</t>
+          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>7207250142-BSS-CTR-2026-020</t>
+          <t>4500010848</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+          <t>Irwan / Budi Bernadi</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Maintenance Superintendent</t>
+          <t>MM Operation Supervisor</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -670,59 +670,55 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7203250036</t>
+          <t>7201250141</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>27 Aug 2026</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27 Aug 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -737,12 +733,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Budi Bernadi / Irwan</t>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MM Operation Supervisor</t>
+          <t>Contract Engineer</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -767,34 +763,26 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01 s/d 31 Juli 2026</t>
+          <t>18 sd 20 Mei 2026</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>4500010848</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>27 Aug 2026</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4500010848</t>
-        </is>
-      </c>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
           <t>100%</t>
@@ -812,12 +800,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Irwan / Budi Bernadi</t>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>MM Operation Supervisor</t>
+          <t>Contract Engineer</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -828,14 +816,14 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,7 +838,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -865,7 +853,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -876,7 +864,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -921,23 +909,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18 sd 20 Mei 2026</t>
+          <t>15 Juli sd 11 Agustus 2026</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>014/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>11 Aug 2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -958,14 +946,10 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Contract Engineer</t>
-        </is>
-      </c>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
           <t>--- (Tidak Ada / Kosong) ---</t>
@@ -974,14 +958,14 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -996,7 +980,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1011,7 +995,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1022,7 +1006,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>06 Jul 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1067,23 +1051,23 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>15 Juli sd 11 Agustus 2026</t>
+          <t>06 sd 09 Juli 2026</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/WS/VIII/2026</t>
+          <t>008/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>11 Aug 2026</t>
+          <t>09 Jul 2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Senoro 2 ke Batam</t>
+          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1104,10 +1088,14 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
       <c r="AD5" t="inlineStr">
         <is>
           <t>--- (Tidak Ada / Kosong) ---</t>
@@ -1116,14 +1104,14 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1138,7 +1126,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1153,7 +1141,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,7 +1152,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>06 Jul 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1209,23 +1197,27 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>06 sd 09 Juli 2026</t>
+          <t>03 sd 04 Agustus 2026</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>09 Jul 2026</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr"/>
+          <t>04 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1262,14 +1254,14 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1284,7 +1276,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1294,12 +1286,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>05 Aug 2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1307,7 +1299,11 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>03 Aug 2026</t>
@@ -1355,27 +1351,23 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03 sd 04 Agustus 2026</t>
+          <t>5 Agustus  2026</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
+          <t>05 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1412,14 +1404,14 @@
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1434,22 +1426,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17 Dec 2025</t>
+          <t>08 Sep 2026</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1457,14 +1449,10 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4500011586</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1509,23 +1497,23 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>5 Agustus  2026</t>
+          <t>16 Agustus 2026</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>05 Aug 2026</t>
+          <t>16 Aug 2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1562,14 +1550,14 @@
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1584,22 +1572,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08 Sep 2026</t>
+          <t>17 Dec 2025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1610,7 +1598,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1655,23 +1643,23 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>16 Agustus 2026</t>
+          <t>8 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>16 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1708,14 +1696,14 @@
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1730,7 +1718,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1745,7 +1733,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1753,10 +1741,14 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4500011682</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1801,23 +1793,23 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>8 sd 31 Agustus 2026</t>
+          <t>25  Agustus  2026</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Food &amp; beverage, main course ,Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1854,14 +1846,14 @@
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1876,7 +1868,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Penyediaan electric cable pendukung wellservice camp</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1891,7 +1883,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1901,12 +1893,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4500011682</t>
+          <t>4500011581</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1951,23 +1943,23 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>25  Agustus  2026</t>
+          <t>17 Januari 2026</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>001/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>17 Jan 2026</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Penyediaan electric cable pendukung wellservice camp</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -2004,14 +1996,14 @@
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014A/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2026,7 +2018,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2036,12 +2028,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2049,14 +2041,10 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4500011581</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>01 Jul 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2101,23 +2089,23 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>17 Januari 2026</t>
+          <t>28 sd 31 Juli 2026</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/WS/I/2026</t>
+          <t>014A/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>17 Jan 2026</t>
+          <t>31 Jul 2026</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -2138,14 +2126,10 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Contract Engineer</t>
-        </is>
-      </c>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
           <t>--- (Tidak Ada / Kosong) ---</t>
@@ -2154,14 +2138,14 @@
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>014A/BSS-JOB/WS/VII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2176,7 +2160,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2186,12 +2170,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2199,10 +2183,14 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>01 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2247,23 +2235,23 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>28 sd 31 Juli 2026</t>
+          <t>17 Januari 2026</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>014A/BSS-JOB/WS/VII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>31 Jul 2026</t>
+          <t>30 Jan 2026</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Pengiriman X-Mas Tree dari Pelabuhan Surabaya ke Pelabuhan Sunda Kelapa di Jakarta</t>
+          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -2284,10 +2272,14 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>--- (Tidak Ada / Kosong) ---</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr"/>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
       <c r="AD13" t="inlineStr">
         <is>
           <t>--- (Tidak Ada / Kosong) ---</t>
@@ -2296,14 +2288,14 @@
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2318,7 +2310,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2333,7 +2325,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2348,7 +2340,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2393,12 +2385,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>17 Januari 2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2409,7 +2401,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Material Pendukung Pekerjaan Sealant Cluster B</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -2446,14 +2438,14 @@
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2468,7 +2460,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2483,7 +2475,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2493,12 +2485,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011683</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>24 Aug 2026</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2543,23 +2535,27 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>25  Agustus  2026</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>30 Jan 2026</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4500011683</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -2596,14 +2592,14 @@
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>018/BSS-JOB/WS/VIII/2026</t>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2618,7 +2614,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2633,7 +2629,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25 Aug 2026</t>
+          <t>26 Aug 2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2641,79 +2637,75 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24 Aug 2026</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Contract Engineer</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>25  Agustus  2026</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>4500011683</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>24 Aug 2026</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Contract Engineer</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>PT Banggai Sentral Sulawesi</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Ir. Ferry Tatimu</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>25  Agustus  2026</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>018/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>25 Aug 2026</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>4500011683</t>
-        </is>
-      </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -2750,14 +2742,14 @@
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>019/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2772,7 +2764,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2787,7 +2779,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2795,10 +2787,14 @@
           <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24 Aug 2026</t>
+          <t>03 Sep 2026</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2843,27 +2839,23 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>25  Agustus  2026</t>
+          <t>10 Agustus 2026</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>019/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>26 Aug 2026</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>4500011683</t>
-        </is>
-      </c>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -2900,14 +2892,14 @@
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2922,7 +2914,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2997,12 +2989,12 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>10 Agustus 2026</t>
+          <t>4 September 2026</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -3013,7 +3005,7 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -3050,14 +3042,14 @@
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3072,7 +3064,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3152,7 +3144,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3163,7 +3155,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen dan pengiriman ke Lokasi Senoro</t>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -3200,14 +3192,14 @@
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3222,7 +3214,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3237,7 +3229,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3252,7 +3244,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>03 Sep 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3297,23 +3289,23 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>4 September 2026</t>
+          <t>Periode tanggal 8 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>023/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -3350,14 +3342,14 @@
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3447,12 +3439,12 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Periode tanggal 8 sd 31 Agustus 2026</t>
+          <t>Periode Tanggal 8 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VII/2026</t>
+          <t>024/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3500,14 +3492,14 @@
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3522,7 +3514,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3597,12 +3589,12 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Periode Tanggal 8 sd 31 Agustus 2026</t>
+          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VII/2026</t>
+          <t>025/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3613,7 +3605,7 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -3650,14 +3642,14 @@
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3672,7 +3664,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3702,7 +3694,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>06 Aug 2026</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3747,12 +3739,12 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
+          <t>Periode tanggal 07 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VII/2026</t>
+          <t>026/BSS-JOB/WS/VII/2026</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3763,7 +3755,7 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -3800,14 +3792,14 @@
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3822,7 +3814,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3852,7 +3844,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>06 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3902,7 +3894,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3913,7 +3905,7 @@
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -3950,14 +3942,14 @@
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3972,7 +3964,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4047,12 +4039,12 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Periode tanggal 07 sd 31 Agustus 2026</t>
+          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -4063,7 +4055,7 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -4100,14 +4092,14 @@
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4122,7 +4114,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4202,7 +4194,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4213,7 +4205,7 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -4250,14 +4242,14 @@
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4272,7 +4264,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4287,7 +4279,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4297,12 +4289,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011236</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>18 Feb 2026</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4347,23 +4339,23 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Periode tanggal 08 sd 31 Agustus 2026</t>
+          <t>2026/04/28</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>28 Apr 2026</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -4400,14 +4392,14 @@
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4422,7 +4414,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4437,7 +4429,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4447,12 +4439,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4500011236</t>
+          <t>4500011203</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18 Feb 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4497,23 +4489,23 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>2026/04/28</t>
+          <t>19 Februari 2026</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>28 Apr 2026</t>
+          <t>19 Feb 2026</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -4550,14 +4542,14 @@
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4572,7 +4564,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4582,12 +4574,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4597,12 +4589,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4500011203</t>
+          <t>4500011579</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>04 Jun 2026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4647,23 +4639,23 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>19 Februari 2026</t>
+          <t>18 sd 20 Mei 2026</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>19 Feb 2026</t>
+          <t>06 Jun 2026</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -4700,14 +4692,14 @@
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4722,7 +4714,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4747,7 +4739,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4500011579</t>
+          <t>4500011580</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4797,12 +4789,12 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>18 sd 20 Mei 2026</t>
+          <t>Periode tanggal 6 Juni 2026</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4813,7 +4805,7 @@
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -4850,59 +4842,59 @@
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7201250141</t>
+          <t>7207250142</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>17 Dec 2025</t>
+          <t>08 Sep 2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06 Jun 2026</t>
+          <t>31 Dec 2025</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4500011580</t>
+          <t>4599910747</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>04 Jun 2026</t>
+          <t>20 Dec 2025</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4917,12 +4909,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Contract Engineer</t>
+          <t>Maintenance Support Supervisor</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -4932,7 +4924,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Jl. Urip Sumorharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -4947,26 +4939,34 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Periode tanggal 6 Juni 2026</t>
+          <t>sd 31 Desember 2025</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>001-TOMORI-FLD-BSS- WCC-2025</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>06 Jun 2026</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr"/>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>001-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
           <t>100%</t>
@@ -4984,12 +4984,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Aldito Fauzi Roe / Aryanto Yoga</t>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Contract Engineer</t>
+          <t>Maintenance Superintendent</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5000,7 +5000,2535 @@
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>2026-09-10 13:41:11</t>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4500010748</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>20 sd 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>002-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>002-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>20 sd 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>003-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>JJasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>003-TOMORI-FLD-BSS-CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>20 sd 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>004-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>004-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4500010746</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>20 sd 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>005-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>asa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>005-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>4500010745</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>20 sd 31 Desember 2025</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>006-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>31 Dec 2025</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>006-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>007/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4500010745</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>01 sd 31 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>006A-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>006-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>008/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>01 sd 31 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>003A-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>003-TOMORI-FLD-BSS-CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>009/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4500010746</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>01 sd 31 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>005A-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>005-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>010/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4500010748</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>01 sd 31 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>002A-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>002-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>01 sd 31 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>004A-TOMORI-FLD-BSS- WCC-2025</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>31 Jan 2026</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>004-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/FLD/I/2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4500010980</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>03 Feb 2026</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3 sd 9 Februari 2026</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>008-TOMORI-FLD-BSS- WCC-2026</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>10 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2025-008</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>008-TOMORI-FLD-BSS- CTR-2026</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4500010748</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1 sd 28 Februari 2026</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>'7207250142-BSS-WCC-2026-002C</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>002-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>014/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JJasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4500010749</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1 sd 28 Februari 2026</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WCC-2026-003C</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>003-TOMORI-FLD-BSS-CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>015/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4500010750</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>01 sd 31 Januari 2026</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WCC-2026-004C</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>004-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>016/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4500010746</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>01 sd 28 Februari 2026</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WCC-2026-005C</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>005-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>017/BSS-JOB/FLD/II/2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7207250142</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>S250551FLD-R1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>24 Month</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4500010745</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>20 Dec 2025</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Rafik Hidayat / Ronny Dwi Purnomo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Maintenance Support Supervisor</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>PT Banggai Sentral Sulawesi</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Jl. Urip Sumoharjo No. 53, Luwuk, Kabupaten Banggai, Provinsi Sulawesi Tengah (94715), Indonesia</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Ir. Ferry Tatimu</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>01 sd 28 Februari 2026</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WCC-2026-006C</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>28 Feb 2026</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>006-TOMORI-FLD-BSS- CTR-2025</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Onesimus Suriadi</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Manager General Services</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Imron Maulana / Moh Bazarul Aqhsa</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Maintenance Superintendent</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>--- (Tidak Ada / Kosong) ---</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>2026-09-10 19:02:53</t>
         </is>
       </c>
     </row>
